--- a/artfynd/A 41185-2024 artfynd.xlsx
+++ b/artfynd/A 41185-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY58"/>
+  <dimension ref="A1:AY62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125130143</v>
+        <v>125129943</v>
       </c>
       <c r="B2" t="n">
-        <v>80071</v>
+        <v>79359</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2081</v>
+        <v>185</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,13 +710,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>461019</v>
+        <v>460966</v>
       </c>
       <c r="R2" t="n">
-        <v>6864146</v>
+        <v>6864145</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125129818</v>
+        <v>125129678</v>
       </c>
       <c r="B3" t="n">
-        <v>80071</v>
+        <v>80433</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,13 +807,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>460961</v>
+        <v>460939</v>
       </c>
       <c r="R3" t="n">
-        <v>6864132</v>
+        <v>6864105</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -869,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125132660</v>
+        <v>125129818</v>
       </c>
       <c r="B4" t="n">
-        <v>98324</v>
+        <v>80433</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>2081</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>461294</v>
+        <v>460961</v>
       </c>
       <c r="R4" t="n">
-        <v>6864095</v>
+        <v>6864132</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125132580</v>
+        <v>125129996</v>
       </c>
       <c r="B5" t="n">
-        <v>98324</v>
+        <v>80433</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>2081</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,13 +1001,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>461296</v>
+        <v>460975</v>
       </c>
       <c r="R5" t="n">
-        <v>6864093</v>
+        <v>6864163</v>
       </c>
       <c r="S5" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1063,54 +1063,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125131600</v>
+        <v>125130143</v>
       </c>
       <c r="B6" t="n">
-        <v>98324</v>
+        <v>80433</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>2081</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Digerbäcken Härjåsjön, Digerbäcken Härjåsjön, Hjd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>461146</v>
+        <v>461019</v>
       </c>
       <c r="R6" t="n">
-        <v>6864118</v>
+        <v>6864146</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1169,10 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125131629</v>
+        <v>125129411</v>
       </c>
       <c r="B7" t="n">
-        <v>98324</v>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1180,43 +1171,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Digerbäcken Härjåsjön, Digerbäcken Härjåsjön, Hjd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>461139</v>
+        <v>460858</v>
       </c>
       <c r="R7" t="n">
-        <v>6864113</v>
+        <v>6864121</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1278,11 +1260,11 @@
         <v>125129468</v>
       </c>
       <c r="B8" t="n">
-        <v>78967</v>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1372,32 +1354,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125129678</v>
+        <v>125129515</v>
       </c>
       <c r="B9" t="n">
-        <v>80071</v>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1407,13 +1389,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>460939</v>
+        <v>460908</v>
       </c>
       <c r="R9" t="n">
-        <v>6864105</v>
+        <v>6864095</v>
       </c>
       <c r="S9" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1472,11 +1454,11 @@
         <v>125132284</v>
       </c>
       <c r="B10" t="n">
-        <v>78967</v>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -1566,57 +1548,48 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125133270</v>
+        <v>125132137</v>
       </c>
       <c r="B11" t="n">
-        <v>98324</v>
+        <v>79084</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Digerbäcken Härjåsjön, Digerbäcken Härjåsjön, Hjd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>461238</v>
+        <v>461209</v>
       </c>
       <c r="R11" t="n">
-        <v>6864088</v>
+        <v>6864143</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1672,54 +1645,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125130922</v>
+        <v>125131062</v>
       </c>
       <c r="B12" t="n">
-        <v>98324</v>
+        <v>80432</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Digerbäcken Härjåsjön, Digerbäcken Härjåsjön, Hjd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>461045</v>
+        <v>461011</v>
       </c>
       <c r="R12" t="n">
-        <v>6864077</v>
+        <v>6864094</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1752,6 +1716,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Sälg som fått sig en bredsida av skogsmaskin.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1778,57 +1747,48 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125131966</v>
+        <v>125130133</v>
       </c>
       <c r="B13" t="n">
-        <v>98324</v>
+        <v>80461</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Digerbäcken Härjåsjön, Digerbäcken Härjåsjön, Hjd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>461173</v>
+        <v>461023</v>
       </c>
       <c r="R13" t="n">
-        <v>6864136</v>
+        <v>6864126</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1884,10 +1844,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125130751</v>
+        <v>125129067</v>
       </c>
       <c r="B14" t="n">
-        <v>98324</v>
+        <v>99118</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1912,17 +1872,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Digerbäcken Härjåsjön, Digerbäcken Härjåsjön, Hjd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>461061</v>
+        <v>460823</v>
       </c>
       <c r="R14" t="n">
-        <v>6864088</v>
+        <v>6864092</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1981,45 +1950,54 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125129515</v>
+        <v>125129160</v>
       </c>
       <c r="B15" t="n">
-        <v>78967</v>
+        <v>99118</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Digerbäcken Härjåsjön, Digerbäcken Härjåsjön, Hjd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>460908</v>
+        <v>460825</v>
       </c>
       <c r="R15" t="n">
-        <v>6864095</v>
+        <v>6864078</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2052,6 +2030,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Inom anmälan A 41185-2024.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2078,10 +2061,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125133128</v>
+        <v>125129214</v>
       </c>
       <c r="B16" t="n">
-        <v>98324</v>
+        <v>99118</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2106,17 +2089,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Digerbäcken Härjåsjön, Digerbäcken Härjåsjön, Hjd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>461241</v>
+        <v>460832</v>
       </c>
       <c r="R16" t="n">
-        <v>6864122</v>
+        <v>6864071</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2175,10 +2167,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125131751</v>
+        <v>125129317</v>
       </c>
       <c r="B17" t="n">
-        <v>98324</v>
+        <v>99118</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2219,10 +2211,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>461151</v>
+        <v>460840</v>
       </c>
       <c r="R17" t="n">
-        <v>6864121</v>
+        <v>6864071</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2281,10 +2273,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125131767</v>
+        <v>125130234</v>
       </c>
       <c r="B18" t="n">
-        <v>98324</v>
+        <v>99118</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2309,17 +2301,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Digerbäcken Härjåsjön, Digerbäcken Härjåsjön, Hjd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>461147</v>
+        <v>461025</v>
       </c>
       <c r="R18" t="n">
-        <v>6864118</v>
+        <v>6864152</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2352,6 +2353,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>I hyggeskant. Ingen prognos för överlevnad.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2378,10 +2384,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125133086</v>
+        <v>125130368</v>
       </c>
       <c r="B19" t="n">
-        <v>98324</v>
+        <v>99118</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2408,7 +2414,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2422,10 +2428,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>461246</v>
+        <v>461040</v>
       </c>
       <c r="R19" t="n">
-        <v>6864109</v>
+        <v>6864151</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2458,6 +2464,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ute på hygge.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2484,10 +2495,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125133223</v>
+        <v>125130480</v>
       </c>
       <c r="B20" t="n">
-        <v>98324</v>
+        <v>99118</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2512,17 +2523,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Digerbäcken Härjåsjön, Digerbäcken Härjåsjön, Hjd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>461229</v>
+        <v>461080</v>
       </c>
       <c r="R20" t="n">
-        <v>6864100</v>
+        <v>6864109</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2555,6 +2575,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Inom pågående avverkning 41185-2024.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2581,10 +2606,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125130982</v>
+        <v>125130516</v>
       </c>
       <c r="B21" t="n">
-        <v>98324</v>
+        <v>99118</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2609,26 +2634,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Digerbäcken Härjåsjön, Digerbäcken Härjåsjön, Hjd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>461044</v>
+        <v>461082</v>
       </c>
       <c r="R21" t="n">
-        <v>6864085</v>
+        <v>6864100</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2687,10 +2703,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125133715</v>
+        <v>125130552</v>
       </c>
       <c r="B22" t="n">
-        <v>98324</v>
+        <v>99118</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2717,7 +2733,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -2731,10 +2747,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>460973</v>
+        <v>461080</v>
       </c>
       <c r="R22" t="n">
-        <v>6863826</v>
+        <v>6864095</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2793,10 +2809,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125130368</v>
+        <v>125130695</v>
       </c>
       <c r="B23" t="n">
-        <v>98324</v>
+        <v>99118</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2823,7 +2839,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -2837,10 +2853,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>461040</v>
+        <v>461073</v>
       </c>
       <c r="R23" t="n">
-        <v>6864151</v>
+        <v>6864091</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2873,11 +2889,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-05-16</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ute på hygge.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2904,10 +2915,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125130516</v>
+        <v>125130751</v>
       </c>
       <c r="B24" t="n">
-        <v>98324</v>
+        <v>99118</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2939,10 +2950,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>461082</v>
+        <v>461061</v>
       </c>
       <c r="R24" t="n">
-        <v>6864100</v>
+        <v>6864088</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3001,10 +3012,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125132494</v>
+        <v>125130922</v>
       </c>
       <c r="B25" t="n">
-        <v>98324</v>
+        <v>99118</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3029,17 +3040,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr"/>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Digerbäcken Härjåsjön, Digerbäcken Härjåsjön, Hjd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>461285</v>
+        <v>461045</v>
       </c>
       <c r="R25" t="n">
-        <v>6864137</v>
+        <v>6864077</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3098,48 +3118,57 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125130133</v>
+        <v>125130982</v>
       </c>
       <c r="B26" t="n">
-        <v>80099</v>
+        <v>99118</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Digerbäcken Härjåsjön, Digerbäcken Härjåsjön, Hjd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>461023</v>
+        <v>461044</v>
       </c>
       <c r="R26" t="n">
-        <v>6864126</v>
+        <v>6864085</v>
       </c>
       <c r="S26" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3195,10 +3224,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125130552</v>
+        <v>125131278</v>
       </c>
       <c r="B27" t="n">
-        <v>98324</v>
+        <v>99118</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3225,7 +3254,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -3239,10 +3268,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>461080</v>
+        <v>461091</v>
       </c>
       <c r="R27" t="n">
-        <v>6864095</v>
+        <v>6864093</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3301,10 +3330,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125130695</v>
+        <v>125131307</v>
       </c>
       <c r="B28" t="n">
-        <v>98324</v>
+        <v>99118</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3331,7 +3360,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -3345,10 +3374,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>461073</v>
+        <v>461108</v>
       </c>
       <c r="R28" t="n">
-        <v>6864091</v>
+        <v>6864088</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3407,10 +3436,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125131376</v>
+        <v>125131324</v>
       </c>
       <c r="B29" t="n">
-        <v>98324</v>
+        <v>99118</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3451,10 +3480,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>461109</v>
+        <v>461105</v>
       </c>
       <c r="R29" t="n">
-        <v>6864114</v>
+        <v>6864105</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3513,10 +3542,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125131401</v>
+        <v>125131339</v>
       </c>
       <c r="B30" t="n">
-        <v>98324</v>
+        <v>99118</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3541,17 +3570,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr"/>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Digerbäcken Härjåsjön, Digerbäcken Härjåsjön, Hjd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>461116</v>
+        <v>461113</v>
       </c>
       <c r="R30" t="n">
-        <v>6864111</v>
+        <v>6864103</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3610,10 +3648,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125132058</v>
+        <v>125131376</v>
       </c>
       <c r="B31" t="n">
-        <v>98324</v>
+        <v>99118</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3640,7 +3678,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -3654,10 +3692,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>461198</v>
+        <v>461109</v>
       </c>
       <c r="R31" t="n">
-        <v>6864143</v>
+        <v>6864114</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3716,10 +3754,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125132629</v>
+        <v>125131401</v>
       </c>
       <c r="B32" t="n">
-        <v>98324</v>
+        <v>99118</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3751,13 +3789,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>461291</v>
+        <v>461116</v>
       </c>
       <c r="R32" t="n">
-        <v>6864069</v>
+        <v>6864111</v>
       </c>
       <c r="S32" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3813,10 +3851,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125132909</v>
+        <v>125131476</v>
       </c>
       <c r="B33" t="n">
-        <v>98324</v>
+        <v>99118</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3841,17 +3879,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr"/>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Digerbäcken Härjåsjön, Digerbäcken Härjåsjön, Hjd</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>461292</v>
+        <v>461128</v>
       </c>
       <c r="R33" t="n">
-        <v>6864106</v>
+        <v>6864104</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3910,10 +3957,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125131324</v>
+        <v>125131512</v>
       </c>
       <c r="B34" t="n">
-        <v>98324</v>
+        <v>99118</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3940,7 +3987,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -3954,10 +4001,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>461105</v>
+        <v>461130</v>
       </c>
       <c r="R34" t="n">
-        <v>6864105</v>
+        <v>6864109</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4016,10 +4063,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125131722</v>
+        <v>125131564</v>
       </c>
       <c r="B35" t="n">
-        <v>98324</v>
+        <v>99118</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4060,10 +4107,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>461152</v>
+        <v>461119</v>
       </c>
       <c r="R35" t="n">
-        <v>6864090</v>
+        <v>6864111</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4122,10 +4169,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125133108</v>
+        <v>125131600</v>
       </c>
       <c r="B36" t="n">
-        <v>98324</v>
+        <v>99118</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4166,10 +4213,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>461245</v>
+        <v>461146</v>
       </c>
       <c r="R36" t="n">
-        <v>6864117</v>
+        <v>6864118</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4228,10 +4275,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125129317</v>
+        <v>125131629</v>
       </c>
       <c r="B37" t="n">
-        <v>98324</v>
+        <v>99118</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4258,7 +4305,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -4272,10 +4319,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>460840</v>
+        <v>461139</v>
       </c>
       <c r="R37" t="n">
-        <v>6864071</v>
+        <v>6864113</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4334,45 +4381,54 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125131062</v>
+        <v>125131653</v>
       </c>
       <c r="B38" t="n">
-        <v>80070</v>
+        <v>99118</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Digerbäcken Härjåsjön, Digerbäcken Härjåsjön, Hjd</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>461011</v>
+        <v>461143</v>
       </c>
       <c r="R38" t="n">
-        <v>6864094</v>
+        <v>6864105</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4405,11 +4461,6 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-05-16</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Sälg som fått sig en bredsida av skogsmaskin.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4436,10 +4487,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125133925</v>
+        <v>125131722</v>
       </c>
       <c r="B39" t="n">
-        <v>98324</v>
+        <v>99118</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4466,7 +4517,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -4480,10 +4531,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>460993</v>
+        <v>461152</v>
       </c>
       <c r="R39" t="n">
-        <v>6863775</v>
+        <v>6864090</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4542,10 +4593,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125131339</v>
+        <v>125131751</v>
       </c>
       <c r="B40" t="n">
-        <v>98324</v>
+        <v>99118</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4586,10 +4637,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>461113</v>
+        <v>461151</v>
       </c>
       <c r="R40" t="n">
-        <v>6864103</v>
+        <v>6864121</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4648,10 +4699,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125130234</v>
+        <v>125131767</v>
       </c>
       <c r="B41" t="n">
-        <v>98324</v>
+        <v>99118</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4676,26 +4727,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Digerbäcken Härjåsjön, Digerbäcken Härjåsjön, Hjd</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>461025</v>
+        <v>461147</v>
       </c>
       <c r="R41" t="n">
-        <v>6864152</v>
+        <v>6864118</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4728,11 +4770,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-05-16</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>I hyggeskant. Ingen prognos för överlevnad.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4759,10 +4796,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125131920</v>
+        <v>125131820</v>
       </c>
       <c r="B42" t="n">
-        <v>98324</v>
+        <v>99118</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4787,26 +4824,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Digerbäcken Härjåsjön, Digerbäcken Härjåsjön, Hjd</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>461175</v>
+        <v>461156</v>
       </c>
       <c r="R42" t="n">
-        <v>6864139</v>
+        <v>6864121</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4865,10 +4893,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125133411</v>
+        <v>125131920</v>
       </c>
       <c r="B43" t="n">
-        <v>98324</v>
+        <v>99118</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4895,7 +4923,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -4909,10 +4937,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>461135</v>
+        <v>461175</v>
       </c>
       <c r="R43" t="n">
-        <v>6864069</v>
+        <v>6864139</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4971,10 +4999,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125129160</v>
+        <v>125131966</v>
       </c>
       <c r="B44" t="n">
-        <v>98324</v>
+        <v>99118</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5001,7 +5029,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -5015,10 +5043,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>460825</v>
+        <v>461173</v>
       </c>
       <c r="R44" t="n">
-        <v>6864078</v>
+        <v>6864136</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5051,11 +5079,6 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-05-16</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Inom anmälan A 41185-2024.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5082,10 +5105,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125131307</v>
+        <v>125132058</v>
       </c>
       <c r="B45" t="n">
-        <v>98324</v>
+        <v>99118</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5112,7 +5135,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -5126,10 +5149,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>461108</v>
+        <v>461198</v>
       </c>
       <c r="R45" t="n">
-        <v>6864088</v>
+        <v>6864143</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5188,10 +5211,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125129214</v>
+        <v>125132112</v>
       </c>
       <c r="B46" t="n">
-        <v>98324</v>
+        <v>99118</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5218,7 +5241,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -5232,10 +5255,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>460832</v>
+        <v>461197</v>
       </c>
       <c r="R46" t="n">
-        <v>6864071</v>
+        <v>6864138</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5294,10 +5317,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125131278</v>
+        <v>125132494</v>
       </c>
       <c r="B47" t="n">
-        <v>98324</v>
+        <v>99118</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5322,26 +5345,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Digerbäcken Härjåsjön, Digerbäcken Härjåsjön, Hjd</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>461091</v>
+        <v>461285</v>
       </c>
       <c r="R47" t="n">
-        <v>6864093</v>
+        <v>6864137</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5400,10 +5414,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125132743</v>
+        <v>125132580</v>
       </c>
       <c r="B48" t="n">
-        <v>98324</v>
+        <v>99118</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5428,29 +5442,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Digerbäcken Härjåsjön, Digerbäcken Härjåsjön, Hjd</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>461322</v>
+        <v>461296</v>
       </c>
       <c r="R48" t="n">
-        <v>6864059</v>
+        <v>6864093</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5506,10 +5511,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125131512</v>
+        <v>125132629</v>
       </c>
       <c r="B49" t="n">
-        <v>98324</v>
+        <v>99118</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5534,29 +5539,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Digerbäcken Härjåsjön, Digerbäcken Härjåsjön, Hjd</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>461130</v>
+        <v>461291</v>
       </c>
       <c r="R49" t="n">
-        <v>6864109</v>
+        <v>6864069</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5612,10 +5608,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125131564</v>
+        <v>125132660</v>
       </c>
       <c r="B50" t="n">
-        <v>98324</v>
+        <v>99118</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5640,26 +5636,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Digerbäcken Härjåsjön, Digerbäcken Härjåsjön, Hjd</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>461119</v>
+        <v>461294</v>
       </c>
       <c r="R50" t="n">
-        <v>6864111</v>
+        <v>6864095</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5718,10 +5705,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125130480</v>
+        <v>125132743</v>
       </c>
       <c r="B51" t="n">
-        <v>98324</v>
+        <v>99118</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5762,10 +5749,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>461080</v>
+        <v>461322</v>
       </c>
       <c r="R51" t="n">
-        <v>6864109</v>
+        <v>6864059</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5798,11 +5785,6 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-05-16</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Inom pågående avverkning 41185-2024.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5829,48 +5811,57 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125132137</v>
+        <v>125132862</v>
       </c>
       <c r="B52" t="n">
-        <v>78725</v>
+        <v>99118</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Digerbäcken Härjåsjön, Digerbäcken Härjåsjön, Hjd</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>461209</v>
+        <v>461261</v>
       </c>
       <c r="R52" t="n">
-        <v>6864143</v>
+        <v>6864090</v>
       </c>
       <c r="S52" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -5926,10 +5917,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125131820</v>
+        <v>125132909</v>
       </c>
       <c r="B53" t="n">
-        <v>98324</v>
+        <v>99118</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5961,10 +5952,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>461156</v>
+        <v>461292</v>
       </c>
       <c r="R53" t="n">
-        <v>6864121</v>
+        <v>6864106</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6026,7 +6017,7 @@
         <v>125133034</v>
       </c>
       <c r="B54" t="n">
-        <v>98324</v>
+        <v>99118</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6129,10 +6120,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125132112</v>
+        <v>125133086</v>
       </c>
       <c r="B55" t="n">
-        <v>98324</v>
+        <v>99118</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6173,10 +6164,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>461197</v>
+        <v>461246</v>
       </c>
       <c r="R55" t="n">
-        <v>6864138</v>
+        <v>6864109</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6235,10 +6226,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125132862</v>
+        <v>125133108</v>
       </c>
       <c r="B56" t="n">
-        <v>98324</v>
+        <v>99118</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6265,7 +6256,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -6279,10 +6270,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>461261</v>
+        <v>461245</v>
       </c>
       <c r="R56" t="n">
-        <v>6864090</v>
+        <v>6864117</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6341,10 +6332,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125131653</v>
+        <v>125133128</v>
       </c>
       <c r="B57" t="n">
-        <v>98324</v>
+        <v>99118</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6369,26 +6360,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Digerbäcken Härjåsjön, Digerbäcken Härjåsjön, Hjd</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>461143</v>
+        <v>461241</v>
       </c>
       <c r="R57" t="n">
-        <v>6864105</v>
+        <v>6864122</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6447,10 +6429,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125131476</v>
+        <v>125133223</v>
       </c>
       <c r="B58" t="n">
-        <v>98324</v>
+        <v>99118</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6475,26 +6457,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Digerbäcken Härjåsjön, Digerbäcken Härjåsjön, Hjd</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>461128</v>
+        <v>461229</v>
       </c>
       <c r="R58" t="n">
-        <v>6864104</v>
+        <v>6864100</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6550,6 +6523,430 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>125133270</v>
+      </c>
+      <c r="B59" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Digerbäcken Härjåsjön, Digerbäcken Härjåsjön, Hjd</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>461238</v>
+      </c>
+      <c r="R59" t="n">
+        <v>6864088</v>
+      </c>
+      <c r="S59" t="n">
+        <v>10</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>125133411</v>
+      </c>
+      <c r="B60" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Digerbäcken Härjåsjön, Digerbäcken Härjåsjön, Hjd</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>461135</v>
+      </c>
+      <c r="R60" t="n">
+        <v>6864069</v>
+      </c>
+      <c r="S60" t="n">
+        <v>10</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>125133715</v>
+      </c>
+      <c r="B61" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Digerbäcken Härjåsjön, Digerbäcken Härjåsjön, Hjd</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>460973</v>
+      </c>
+      <c r="R61" t="n">
+        <v>6863826</v>
+      </c>
+      <c r="S61" t="n">
+        <v>10</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>125133925</v>
+      </c>
+      <c r="B62" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Digerbäcken Härjåsjön, Digerbäcken Härjåsjön, Hjd</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>460993</v>
+      </c>
+      <c r="R62" t="n">
+        <v>6863775</v>
+      </c>
+      <c r="S62" t="n">
+        <v>10</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 41185-2024 artfynd.xlsx
+++ b/artfynd/A 41185-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY62"/>
+  <dimension ref="A1:AZ62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125129943</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125129678</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125129818</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125129996</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125130143</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125129411</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125129468</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125129515</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1545,6 +1590,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125132284</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1642,6 +1692,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125132137</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1744,6 +1799,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125131062</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1841,6 +1901,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125130133</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1947,6 +2012,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125129067</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2058,6 +2128,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125129160</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2164,6 +2239,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125129214</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2270,6 +2350,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125129317</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2381,6 +2466,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125130234</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2492,6 +2582,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125130368</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2603,6 +2698,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125130480</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2700,6 +2800,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125130516</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2806,6 +2911,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125130552</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2912,6 +3022,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125130695</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3009,6 +3124,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125130751</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3115,6 +3235,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125130922</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3221,6 +3346,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125130982</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3327,6 +3457,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125131278</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3433,6 +3568,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125131307</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3539,6 +3679,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125131324</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3645,6 +3790,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125131339</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3751,6 +3901,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125131376</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3848,6 +4003,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125131401</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3954,6 +4114,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125131476</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4060,6 +4225,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125131512</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4166,6 +4336,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125131564</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4272,6 +4447,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125131600</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4378,6 +4558,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125131629</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4484,6 +4669,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125131653</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4590,6 +4780,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125131722</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4696,6 +4891,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125131751</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4793,6 +4993,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125131767</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4890,6 +5095,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125131820</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4996,6 +5206,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125131920</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5102,6 +5317,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125131966</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5208,6 +5428,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125132058</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5314,6 +5539,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125132112</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5411,6 +5641,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125132494</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5508,6 +5743,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125132580</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5605,6 +5845,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125132629</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5702,6 +5947,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125132660</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5808,6 +6058,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125132743</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5914,6 +6169,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125132862</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6011,6 +6271,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125132909</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6117,6 +6382,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125133034</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6223,6 +6493,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125133086</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6329,6 +6604,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125133108</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6426,6 +6706,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125133128</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6523,6 +6808,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125133223</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6629,6 +6919,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125133270</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6735,6 +7030,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125133411</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6841,6 +7141,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125133715</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6947,8 +7252,76 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125133925</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>